--- a/data/seed/portfolio/L-2024-5246/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-5246/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J201"/>
+  <dimension ref="A1:J157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,108 +535,103 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n">
-        <v>8203000</v>
-      </c>
+      <c r="C8" s="2" t="n">
+        <v>8649000</v>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1766 01.07.2026, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №225/26, QQS bilan</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>74003000</v>
+        <v>57151000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46204</v>
+        <v>46208</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n">
-        <v>1211000</v>
-      </c>
+      <c r="C9" s="2" t="n">
+        <v>17200000</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>275025945</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-5246)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>16307000393740656417</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №112/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2024-5246 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>75214000</v>
+        <v>39951000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>6806000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>28597000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qarshi Mebel MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>366471775</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000865802242001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -646,86 +641,91 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №158/26</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1332</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>68408000</v>
+        <v>68548000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>2914000</v>
+        <v>15930000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lazzat Un Mahsulotlari MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>224425383</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000457145574001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7521</t>
+          <t>Оплата за продукцию по договору №107/26, НДС 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>71322000</v>
+        <v>84478000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>17200000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>13088000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-5246)</t>
+          <t>Qarshi Metall Servis AJ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>16307000393740656417</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-5246 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за продукцию по договору №269/26, НДС 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>54122000</v>
+        <v>97566000</v>
       </c>
     </row>
     <row r="13">
@@ -735,378 +735,378 @@
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>3994000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>12308000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>275025945</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shartnoma №100/26 bo'yicha oldindan to'lov</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>58116000</v>
+        <v>85258000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>1580000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>1692000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Farg'ona Qurilish XK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>229430811</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000685610905001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №244/26, НДС 12%</t>
+          <t>Ijara haqi iyul oyi uchun, shartn. №80/23</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>59696000</v>
+        <v>83566000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>1208000</v>
+        <v>17775000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Qo'qon Farm Savdo XK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>239039600</t>
+          <t>302594530</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000785864823001</t>
+          <t>20208000468416691001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9651 06.07.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5012 08.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>60904000</v>
+        <v>101341000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>1186000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>10366000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №201/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №880</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>62090000</v>
+        <v>90975000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n">
-        <v>1173000</v>
+        <v>20653000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Ziyo Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>301976354</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000447280384001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7430</t>
+          <t>Mahsulot uchun to'lov, shartnoma №148/26, QQS 12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>63263000</v>
+        <v>111628000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>983000</v>
+        <v>9456000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shartnoma №126/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №514 10.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>64246000</v>
+        <v>121084000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>1483000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>5458000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Ishonch Plastik XK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>252399089</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000416827903001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №180/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3044 10.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>62763000</v>
+        <v>126542000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>12308000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>11467000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qarshi Metall Servis AJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №1858</t>
+          <t>Mahsulot uchun to'lov, shartnoma №254/26, QQS 12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>50455000</v>
+        <v>138009000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>4647000</v>
+        <v>5934000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8205</t>
+          <t>Tovar uchun to'lov, hisob-faktura №656 13.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>55102000</v>
+        <v>143943000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>2074000</v>
+        <v>2479000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>303960067</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000586482304001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1116,291 +1116,291 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №224/26, НДС 12%</t>
+          <t>Shartnoma №197/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>57176000</v>
+        <v>146422000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1692000</v>
+        <v>1469000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Omad Qurilish Materiallari MChJ</t>
+          <t>Guliston Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>281427485</t>
+          <t>374445546</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000228477497001</t>
+          <t>20208000978719906001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по договору №80/24</t>
+          <t>Оплата за упаковочные материалы, с/ф №8263</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>55484000</v>
+        <v>144953000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>1017000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>2071000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Ziyo Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>239039600</t>
+          <t>318209667</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000785864823001</t>
+          <t>20208000193883478001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7110</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №182/26</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>56501000</v>
+        <v>142882000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>1008000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>3340000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Ziyo Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>239039600</t>
+          <t>318209667</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000785864823001</t>
+          <t>20208000193883478001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SHARTNOMA №55/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за упаковочные материалы, с/ф №2770</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>57509000</v>
+        <v>139542000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>2911000</v>
-      </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n">
+        <v>3779000</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>226970701</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000632089357001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Предоплата за материалы подоговору №260/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №229/26, QQS 12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>54598000</v>
+        <v>143321000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>12083000</v>
+        <v>2836000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5740 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №7586 14.07.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>66681000</v>
+        <v>146157000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>3007000</v>
+        <v>2356000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8670 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5826</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>69688000</v>
+        <v>148513000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>1735000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>7251000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Nurafshon Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>244269707</t>
+          <t>347177508</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000156320893001</t>
+          <t>20208000580224285001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Shartnoma №73/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по дог. №246/26</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>71423000</v>
+        <v>141262000</v>
       </c>
     </row>
     <row r="30">
@@ -1410,157 +1410,157 @@
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>4907000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>52987000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №13/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №180/26, QQS bilan</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>76330000</v>
+        <v>88275000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>8923000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>1678000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Shartnoma №10/26 bo'yicha oldindan to'lov</t>
+          <t>Iyun oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>85253000</v>
+        <v>86597000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>4191000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>1678000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Shartnoma №148/26 bo'yicha oldindan to'lov</t>
+          <t>JShDS iyun oyi uchun</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>89444000</v>
+        <v>84919000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1678000</v>
+        <v>5890000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №63/26, QQS bilan</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>87766000</v>
+        <v>79029000</v>
       </c>
     </row>
     <row r="34">
@@ -1570,37 +1570,37 @@
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>1678000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>39233000</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>НДФЛ за июнь 2026</t>
+          <t>SHARTNOMA №143/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>86088000</v>
+        <v>118262000</v>
       </c>
     </row>
     <row r="35">
@@ -1610,37 +1610,37 @@
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n">
-        <v>4312000</v>
-      </c>
+      <c r="C35" s="2" t="n">
+        <v>1003000</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №151/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №181/26</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>90400000</v>
+        <v>117259000</v>
       </c>
     </row>
     <row r="36">
@@ -1650,1128 +1650,1118 @@
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>2052000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>5244000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №34/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №189/26</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>92452000</v>
+        <v>112015000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>1109000</v>
+        <v>4991000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qo'qon Farm Savdo XK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>302594530</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000468416691001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №193/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4603</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>93561000</v>
+        <v>117006000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>2049000</v>
+        <v>57848000</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Durdona Qog'oz MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>236906530</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000893254047001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №85/26</t>
+          <t>Tovarlar uchun to'lov h/f №6455</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>91512000</v>
+        <v>59158000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>15151000</v>
+        <v>2834000</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bahor Non AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>311072588</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000137778051001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №76/26</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>76361000</v>
+        <v>56324000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>2842000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>8292000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4617 20.07.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №6820</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>79203000</v>
+        <v>48032000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>2296000</v>
+        <v>8394000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chust Yog' Zavodi MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>269530877</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000098978240001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1267 20.07.2026, QQS bilan</t>
+          <t>Оплата по с/ф №9819 за поставленный товар</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>81499000</v>
+        <v>56426000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>1605000</v>
+        <v>2743000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>239039600</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000785864823001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6319 20.07.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3212 24.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>83104000</v>
+        <v>59169000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>1550000</v>
+        <v>8487000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lazzat Un Mahsulotlari MChJ</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>224425383</t>
+          <t>303960067</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000457145574001</t>
+          <t>20208000586482304001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №72/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №21/26, QQS 12%</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>84654000</v>
+        <v>67656000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>2687000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>4450000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Qarshi Mebel MChJ</t>
+          <t>Qo'qon Farm Savdo XK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>366471775</t>
+          <t>302594530</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000865802242001</t>
+          <t>20208000468416691001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №255/26</t>
+          <t>Shartnoma №288/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>81967000</v>
+        <v>72106000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>4344000</v>
-      </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n">
+        <v>4006000</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Durdona Qog'oz MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>236906530</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000893254047001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTN. №264/26</t>
+          <t>Tovar uchun to'lov, h/f №4725 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>77623000</v>
+        <v>76112000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>138311000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>3767000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1558</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №281/26 ОТ 27.07.2026</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>-60688000</v>
+        <v>79879000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>2895000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>1058000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000389038063001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №174/26, НДС 12%</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>-57793000</v>
+        <v>78821000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>1624000</v>
+        <v>2219000</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Qarshi Mebel MChJ</t>
+          <t>Barakali Qurilish MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>366471775</t>
+          <t>315713480</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000865802242001</t>
+          <t>20208000832456015001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №58/26</t>
+          <t>Оплата за транспортные услуги по договору №274/26</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>-59417000</v>
+        <v>76602000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>4545000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>28015000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Navoiy Metall Servis MChJ</t>
+          <t>Oltin Vodiy Mato MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>282523990</t>
+          <t>279510389</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000984168279001</t>
+          <t>20208000678784772001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Shartnoma №256/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №196/26</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>-54872000</v>
+        <v>48587000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>1415000</v>
+        <v>16341000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3615 22.07.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1003</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>-53457000</v>
+        <v>64928000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>2778000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>3942000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Qo'shilgan qymat solig'i iyun oyi</t>
+          <t>Shartnoma №170/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>-56235000</v>
+        <v>68870000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46226</v>
+        <v>46234</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>1394000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>275025945</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №685 от 23.07.2026, в т.ч. НДС 12%</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>-54841000</v>
+        <v>68570000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>99816000</v>
+        <v>7141000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lazzat Un Mahsulotlari MChJ</t>
+          <t>Qo'qon Farm Savdo XK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>224425383</t>
+          <t>302594530</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000457145574001</t>
+          <t>20208000468416691001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №114/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №275/26, QQS 12%</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>44975000</v>
+        <v>75711000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>3750000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>6651000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lazzat Un Mahsulotlari MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>224425383</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000457145574001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №91/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №84/26, QQS bilan</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>48725000</v>
+        <v>69060000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>1783000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>10756000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №254/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №246/26</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>50508000</v>
+        <v>58304000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1058000</v>
+        <v>10975000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000432180980001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №3042</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>49450000</v>
+        <v>47329000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>10226000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>14348000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Bahor Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>242538344</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000714557425001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Shartnoma №13/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №1396</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>59676000</v>
+        <v>32981000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46230</v>
+        <v>46238</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>1752000</v>
+        <v>25834000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Ziyo Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>301976354</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000447280384001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4444</t>
+          <t>Shartnoma №283/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>61428000</v>
+        <v>58815000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46231</v>
+        <v>46239</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>5432000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>4604000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Bahor Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>244269707</t>
+          <t>242538344</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000156320893001</t>
+          <t>20208000714557425001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №18/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №999</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>66860000</v>
+        <v>54211000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>12117000</v>
+        <v>17200000</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>238744455</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-5246)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>16307000393740656417</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №251/26</t>
+          <t>Kredit shartnomasi L-2024-5246 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>54743000</v>
+        <v>37011000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>1322000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>27265000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №273/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №33/26</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>56065000</v>
+        <v>9746000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46233</v>
+        <v>46240</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>1265000</v>
+        <v>5034000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1601</t>
+          <t>Shartnoma №180/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>57330000</v>
+        <v>14780000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>14092000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>4074000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Bahor Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>244269707</t>
+          <t>242538344</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000156320893001</t>
+          <t>20208000714557425001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №49/26, QQS 12%</t>
+          <t>Tovarlar uchun to'lov h/f №7439</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>71422000</v>
+        <v>10706000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>300000</v>
+        <v>11644000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
@@ -2791,157 +2781,157 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>71122000</v>
+        <v>-938000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>7305000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>4223000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>232795103</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000916787847001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1833</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2754 07.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>63817000</v>
+        <v>3285000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>3379000</v>
+        <v>2127000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Ziyo Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>301976354</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000447280384001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Shartnoma №82/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №242/26, НДС 12%</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>67196000</v>
+        <v>5412000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>2871000</v>
+        <v>1601000</v>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Afrosiyob Moy MChJ</t>
+          <t>Farg'ona Qurilish XK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>399506706</t>
+          <t>229430811</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000081921999001</t>
+          <t>20208000685610905001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №106/26, QQS bilan</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>64325000</v>
+        <v>3811000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>2994000</v>
+        <v>4545000</v>
       </c>
       <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bahor Trans Servis MChJ</t>
+          <t>Oltin Vodiy Mato MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>342943081</t>
+          <t>279510389</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000268561090001</t>
+          <t>20208000678784772001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2951,507 +2941,517 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №175/26</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №276/26</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>61331000</v>
+        <v>-734000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>3310000</v>
+        <v>18779000</v>
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Afrosiyob Moy MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>399506706</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000081921999001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №194/26</t>
+          <t>Xom ashyo uchun to'lov, shartn. №228/26, QQS bilan</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>58021000</v>
+        <v>-19513000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>3672000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>4482000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>226970701</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000632089357001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5236</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №112/26, QQS 12%</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>54349000</v>
+        <v>-15031000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>4249000</v>
+        <v>3155000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Shartnoma №179/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №199/26, QQS 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>58598000</v>
+        <v>-11876000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>3997000</v>
+        <v>1693000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №193/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4349 13.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>62595000</v>
+        <v>-10183000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>3527000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>6785000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №56/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №202/26</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>66122000</v>
+        <v>-16968000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46238</v>
+        <v>46251</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>1882000</v>
+        <v>12941000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>239039600</t>
+          <t>303960067</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000785864823001</t>
+          <t>20208000586482304001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6430 04.08.2026, QQS bilan</t>
+          <t>Shartnoma №76/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>68004000</v>
+        <v>-4027000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46239</v>
+        <v>46251</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>5200000</v>
+        <v>10172000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Marg'ilon Logistik MChJ</t>
+          <t>Ishonch Plastik XK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>239157134</t>
+          <t>252399089</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000028324560001</t>
+          <t>20208000416827903001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5731 05.08.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №8124 за поставленный товар</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>73204000</v>
+        <v>6145000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46239</v>
+        <v>46251</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>11644000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>9094000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qarshi Metall Servis AJ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №3024</t>
+          <t>Оплата по счет-фактуре №6386 за поставленный товар</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>61560000</v>
+        <v>15239000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46239</v>
+        <v>46251</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>17200000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>6825000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-5246)</t>
+          <t>Omad Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>303960067</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>16307000393740656417</t>
+          <t>20208000586482304001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-5246 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9817</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>44360000</v>
+        <v>22064000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>3646000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>1588000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №166/26, QQS 12%</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>48006000</v>
+        <v>20476000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>3474000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>1588000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №572 06.08.2026, QQS bilan</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>51480000</v>
+        <v>18888000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>2510000</v>
+        <v>77142000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Qo'qon Farm Savdo XK</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>302594530</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>20208000468416691001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6279</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6004 18.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>53990000</v>
+        <v>96030000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>1601000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>12897000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Omad Qurilish Materiallari MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>281427485</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000228477497001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3461,357 +3461,357 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shart. №80/24</t>
+          <t>Mahsulot uchun to'lov, shartnoma №237/26, QQS 12%</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>52389000</v>
+        <v>108927000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>2056000</v>
+        <v>3451000</v>
       </c>
       <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Durdona Qog'oz MChJ</t>
+          <t>Barakali Qurilish MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>236906530</t>
+          <t>315713480</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000893254047001</t>
+          <t>20208000832456015001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №61/26</t>
+          <t>Предоплата за материалы по договору №214/26</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>50333000</v>
+        <v>105476000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>19276000</v>
+        <v>3829000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>239039600</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000785864823001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Shartnoma №37/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9264</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>69609000</v>
+        <v>109305000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>16244000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>7925000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Ziyo Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>318209667</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000193883478001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №111/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №54/26</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>85853000</v>
+        <v>101380000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>14866000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>8036000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Barakali Qurilish MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>315713480</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000832456015001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Shartnoma №17/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №9/26</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>100719000</v>
+        <v>93344000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n">
-        <v>4381000</v>
-      </c>
+      <c r="C86" s="2" t="n">
+        <v>33729000</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №255/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №218/26</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>105100000</v>
+        <v>59615000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>2478000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>2596000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5542 10.08.2026, QQS bilan</t>
+          <t>QQS iyul 2026 uchun</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>107578000</v>
+        <v>57019000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>2331000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>5247000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №7364</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №52/26</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>109909000</v>
+        <v>51772000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>1894000</v>
+        <v>6366000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Afrosiyob Moy MChJ</t>
+          <t>Oltin Vodiy Mato MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>399506706</t>
+          <t>279510389</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000081921999001</t>
+          <t>20208000678784772001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №98/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №226/26</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>108015000</v>
+        <v>45406000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46245</v>
+        <v>46259</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>1502000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>5859000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Qarshi Mebel MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>366471775</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000865802242001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3821,197 +3821,197 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №159/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №191/26, QQS 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>106513000</v>
+        <v>51265000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46245</v>
+        <v>46259</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>52490000</v>
-      </c>
-      <c r="D91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n">
+        <v>3910000</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5677</t>
+          <t>Shartnoma №264/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>54023000</v>
+        <v>55175000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46246</v>
+        <v>46259</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>2861000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>7474000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lazzat Un Mahsulotlari MChJ</t>
+          <t>Yulduz Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>224425383</t>
+          <t>350670640</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000457145574001</t>
+          <t>20208000192199912001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №103/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №93/26, QQS bilan</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>56884000</v>
+        <v>47701000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46246</v>
+        <v>46261</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>6786000</v>
+        <v>1001000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000389038063001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №2018</t>
+          <t>Elektr energiyasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>50098000</v>
+        <v>46700000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46247</v>
+        <v>46261</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>8923000</v>
-      </c>
+      <c r="C94" s="2" t="n">
+        <v>7331000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №97/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №239/26</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>59021000</v>
+        <v>39369000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46248</v>
+        <v>46265</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>3471000</v>
+        <v>10614000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>303960067</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000586482304001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4021,37 +4021,37 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №4/26, QQS 12%</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №229/26, QQS 12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>62492000</v>
+        <v>49983000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>8112000</v>
+        <v>5606000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>244269707</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000156320893001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4061,517 +4061,507 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Shartnoma №81/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №251/26, НДС 12%</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>70604000</v>
+        <v>55589000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>5486000</v>
+        <v>3717000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>239039600</t>
+          <t>226970701</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000785864823001</t>
+          <t>20208000632089357001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Shartnoma №219/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №219/26, QQS 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>76090000</v>
+        <v>59306000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>3351000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>293657039</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3629 17.08.2026, QQS bilan</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>79441000</v>
+        <v>59006000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46251</v>
+        <v>46266</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>1588000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>2691000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>226970701</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000632089357001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №207/26, QQS 12%</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>77853000</v>
+        <v>61697000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46251</v>
+        <v>46266</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>1588000</v>
+        <v>4813000</v>
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Barakali Qurilish MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>315713480</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000832456015001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
+          <t>Предоплата за материалы по договору №47/26</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>76265000</v>
+        <v>56884000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46251</v>
+        <v>46267</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>3857000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>36447000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>303960067</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000586482304001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №27/26</t>
+          <t>Shartnoma №145/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>72408000</v>
+        <v>93331000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46251</v>
+        <v>46267</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>5419000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>3837000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>303960067</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000586482304001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №38/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8568 02.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>66989000</v>
+        <v>97168000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46251</v>
+        <v>46267</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>7325000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>2625000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №212/26, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5908 02.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>59664000</v>
+        <v>99793000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46253</v>
+        <v>46268</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>32068000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>4867000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>303960067</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000586482304001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №277/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartn. №254/26, QQS 12%</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>27596000</v>
+        <v>104660000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46254</v>
+        <v>46269</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>4321000</v>
+        <v>7999000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Guliston Agro MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>388866289</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000479947758001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №216/26, НДС 12%</t>
+          <t>Shartnoma №182/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>31917000</v>
+        <v>112659000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46255</v>
+        <v>46270</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>2655000</v>
+        <v>17200000</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-5246)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000393740656417</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>Kredit shartnomasi L-2024-5246 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>29262000</v>
+        <v>95459000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46255</v>
+        <v>46272</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>6156000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>16505000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>226970701</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000632089357001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №235/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №277/26, НДС 12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>23106000</v>
+        <v>111964000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46258</v>
+        <v>46272</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>18385000</v>
+        <v>6368000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chust Yog' Zavodi MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>269530877</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000098978240001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1989</t>
+          <t>Shartnoma №105/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>41491000</v>
+        <v>118332000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46258</v>
+        <v>46272</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>7231000</v>
+        <v>3612000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Farovon Qurilish XK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>353087750</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000897824047001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4581,157 +4571,157 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №142/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №158/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>48722000</v>
+        <v>121944000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46258</v>
+        <v>46272</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>5865000</v>
+        <v>2136000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7444</t>
+          <t>Mahsulot uchun to'lov, shartnoma №34/26, QQS 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>54587000</v>
+        <v>124080000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46258</v>
+        <v>46272</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>5639000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>1786000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Farg'ona Qurilish XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>244269707</t>
+          <t>229430811</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000156320893001</t>
+          <t>20208000685610905001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1561</t>
+          <t>Bino ijarasi uchun to'lov sentyabr</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>60226000</v>
+        <v>122294000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46258</v>
+        <v>46272</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>3700000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>6321000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Oltin Vodiy Mato MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>239039600</t>
+          <t>279510389</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000785864823001</t>
+          <t>20208000678784772001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1502</t>
+          <t>Оплата за сырье по договору №268/26 от 07.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>63926000</v>
+        <v>115973000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46258</v>
+        <v>46272</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>2547000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>8054000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Zafar Tikuv MChJ</t>
+          <t>Nurafshon Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>355019763</t>
+          <t>347177508</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000484472803001</t>
+          <t>20208000580224285001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4741,632 +4731,632 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №125/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №82/26, QQS bilan</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>66473000</v>
+        <v>107919000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46258</v>
+        <v>46272</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>2438000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>9279000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3606 24.08.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №7903</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>68911000</v>
+        <v>98640000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46258</v>
+        <v>46272</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>1548000</v>
+        <v>12985000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Qarshi Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>366471775</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000865802242001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №90/26, QQS bilan</t>
+          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>67363000</v>
+        <v>85655000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46258</v>
+        <v>46273</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>2031000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>5969000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Termiz Meva Eksport AJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>303806306</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000640772529001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №238/26</t>
+          <t>Оплата за товар по счет-фактуре №3224 от 08.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>65332000</v>
+        <v>91624000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46258</v>
+        <v>46273</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>15104000</v>
+        <v>5317000</v>
       </c>
       <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №152/26, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №239/26, QQS bilan</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>50228000</v>
+        <v>86307000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46259</v>
+        <v>46274</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>14797000</v>
+        <v>8090000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №177/26 от 25.08.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1124 09.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>65025000</v>
+        <v>94397000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46259</v>
+        <v>46275</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>7823000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>1464000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Ziyo Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>239039600</t>
+          <t>318209667</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000785864823001</t>
+          <t>20208000193883478001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Shartnoma №223/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №73/26</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>72848000</v>
+        <v>92933000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46259</v>
+        <v>46276</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>3089000</v>
+        <v>11297000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>244269707</t>
+          <t>303960067</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000156320893001</t>
+          <t>20208000586482304001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №284 за поставленный товар</t>
+          <t>Shartnoma №118/26 bo'yiha oldindan to'lov</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>75937000</v>
+        <v>104230000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46259</v>
+        <v>46276</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>1001000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>10829000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000432180980001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>Предоплата за товар по договору №143/26 от 11.09.2026</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>74936000</v>
+        <v>115059000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46260</v>
+        <v>46276</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>2196000</v>
+        <v>5984000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qo'qon Farm Savdo XK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>302594530</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000468416691001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Shartnoma №231/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №218/26 от 11.09.2026</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>77132000</v>
+        <v>121043000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46262</v>
+        <v>46276</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>9204000</v>
+        <v>1834000</v>
       </c>
       <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №188/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №153/26</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>67928000</v>
+        <v>119209000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46262</v>
+        <v>46279</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>15220000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>5248000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Durdona Qog'oz MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>236906530</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000893254047001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №268/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №143/26, QQS 12%</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>52708000</v>
+        <v>124457000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46265</v>
+        <v>46279</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>10239000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>3542000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>239039600</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000785864823001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №633 31.08.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №7459</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>62947000</v>
+        <v>120915000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46265</v>
+        <v>46280</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>4075000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>1771000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2616 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Ijtimoiy soliq avgust 2026</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>67022000</v>
+        <v>119144000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46265</v>
+        <v>46280</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>3059000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>1771000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №209/26, QQS 12%</t>
+          <t>JShDS avgust oyi uchun</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>70081000</v>
+        <v>117373000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46265</v>
+        <v>46280</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>2221000</v>
-      </c>
+      <c r="C128" s="2" t="n">
+        <v>5450000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Ziyo Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>318209667</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000193883478001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №171/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №150/26</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>72302000</v>
+        <v>111923000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46265</v>
+        <v>46282</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>3501000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qo'qon Farm Savdo XK</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>302594530</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000468416691001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5376,37 +5366,37 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>HISOB-KASSA XIZMATI UCHUN HAQ</t>
+          <t>Оплата за продукцию по договору №93/26, НДС 12%</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>72002000</v>
+        <v>115424000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46265</v>
+        <v>46282</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>12969000</v>
+        <v>10937000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Ziyo Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>318209667</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000193883478001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5416,432 +5406,437 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3906</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №150/26</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>59033000</v>
+        <v>104487000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46266</v>
+        <v>46283</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>3383000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>17980000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Ziyo Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>301976354</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000447280384001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №140/26, QQS BILAN</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7704</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>55650000</v>
+        <v>122467000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46267</v>
+        <v>46283</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>3024000</v>
+        <v>3181000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Guliston Agro MChJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>388866289</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000479947758001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8476</t>
+          <t>Оплата за товар по счет-фактуре №7618 от 18.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>58674000</v>
+        <v>125648000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46267</v>
+        <v>46286</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>1406000</v>
+        <v>17490000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qo'qon Farm Savdo XK</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>302594530</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000468416691001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Shartnoma №89/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №17/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>60080000</v>
+        <v>143138000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46267</v>
+        <v>46286</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>679000</v>
+        <v>8277000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №218/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №54/26, QQS 12%</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>60759000</v>
+        <v>151415000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46268</v>
+        <v>46286</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>3080000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>2994000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1868</t>
+          <t>QQS avgust 2026 uchun</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>63839000</v>
+        <v>148421000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46268</v>
+        <v>46286</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>688000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>3640000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sarbon Mebel MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>244269707</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000156320893001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №264/26 от 03.09.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №280/26</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>64527000</v>
+        <v>144781000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46269</v>
+        <v>46287</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>1093000</v>
+        <v>3972000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7342 04.09.2026, QQS bilan</t>
+          <t>Shartnoma №92/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>65620000</v>
+        <v>148753000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46269</v>
+        <v>46288</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>665000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>1116000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Chust Yog' Zavodi MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>269530877</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000098978240001</t>
+          <t>20208000389038063001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5223 04.09.2026, QQS bilan</t>
+          <t>Elektr energiyasi uchun to'lov sentyabr</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>66285000</v>
+        <v>147637000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46270</v>
+        <v>46288</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>17200000</v>
+        <v>4573000</v>
       </c>
       <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-5246)</t>
+          <t>Sarbon Mebel XK</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>16307000393740656417</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-5246 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №81/26</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>49085000</v>
+        <v>143064000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46272</v>
+        <v>46288</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>18423000</v>
-      </c>
+      <c r="C140" s="2" t="n">
+        <v>6092000</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Oltin Vodiy Mato MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>279510389</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000678784772001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №8678 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №3351</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>67508000</v>
+        <v>136972000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46272</v>
+        <v>46289</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>1771000</v>
+        <v>6459000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Mehnat Poligraf MChJ</t>
+          <t>Ziyo Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>239039600</t>
+          <t>301976354</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000785864823001</t>
+          <t>20208000447280384001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5851,157 +5846,157 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Shartnoma №292/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4169</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>69279000</v>
+        <v>143431000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46272</v>
+        <v>46289</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>1665000</v>
+        <v>2866000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Shartnoma №291/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnma №164/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>70944000</v>
+        <v>146297000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46272</v>
+        <v>46289</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>1267000</v>
-      </c>
+      <c r="C143" s="2" t="n">
+        <v>40934000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Shartnoma №261/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно счет-фактуре №431</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>72211000</v>
+        <v>105363000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46272</v>
+        <v>46290</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>1124000</v>
-      </c>
+      <c r="C144" s="2" t="n">
+        <v>1314000</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Guliston Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>374445546</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000978719906001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Shartnoma №159/26 bo'yicha oldindan to'lov</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTN. №274/26, QQS BILAN</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>73335000</v>
+        <v>104049000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46272</v>
+        <v>46290</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>1000000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>5059000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Ziyo Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>318209667</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>20208000193883478001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6011,37 +6006,37 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6099</t>
+          <t>Tovarlar uchun to'lovh/f №6921</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>74335000</v>
+        <v>98990000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>623000</v>
+        <v>38189000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Omad Plastik MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>303960067</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000586482304001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6051,2146 +6046,391 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8675 за поставленный товар</t>
+          <t>Оплата за товар по с/ф №602 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>74958000</v>
+        <v>137179000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n">
-        <v>2640000</v>
-      </c>
-      <c r="D147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>3846000</v>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Metall Servis AJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>265703992</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000570584747001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №131/26</t>
+          <t>Shartnoma №81/26 bo'yicha odindan to'lov</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>72318000</v>
+        <v>141025000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>4014000</v>
+        <v>1808000</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
+          <t>Bahor Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>238744455</t>
+          <t>242538344</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000629787199001</t>
+          <t>20208000714557425001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №103/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №32/26, QQS bilan</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>68304000</v>
+        <v>139217000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46272</v>
+        <v>46294</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n">
-        <v>12985000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>3955000</v>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Omad Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>303960067</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000586482304001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Оплата за продукцию по договору №12/26, НДС 12%</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>55319000</v>
+        <v>143172000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46273</v>
+        <v>46294</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>5482000</v>
-      </c>
+      <c r="C150" s="2" t="n">
+        <v>2753000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3157</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №2707</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>60801000</v>
+        <v>140419000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46273</v>
+        <v>46294</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>5021000</v>
-      </c>
+      <c r="C151" s="2" t="n">
+        <v>55588000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Barakali Qurilish MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>275025945</t>
+          <t>315713480</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000064684166001</t>
+          <t>20208000832456015001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Shartnoma №146/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №150/26</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>65822000</v>
+        <v>84831000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46273</v>
+        <v>46295</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="n">
-        <v>742000</v>
+        <v>5241000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Jizzax Savdo XK</t>
+          <t>Qo'qon Farm Savdo XK</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>293657039</t>
+          <t>302594530</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000215705847001</t>
+          <t>20208000468416691001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №173/26, НДС 12%</t>
+          <t>Shartnoma №200/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>66564000</v>
+        <v>90072000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46274</v>
+        <v>46295</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>1786000</v>
+        <v>300000</v>
       </c>
       <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Omad Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>281427485</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000228477497001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov sentyabr</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>64778000</v>
+        <v>89772000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46274</v>
+        <v>46295</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>9784000</v>
+        <v>2222000</v>
       </c>
       <c r="D154" s="2" t="n"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Durdona Qog'oz MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>236906530</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000893254047001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №273/26, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №106/26, QQS bilan</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>54994000</v>
+        <v>87550000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46275</v>
+        <v>46295</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>2571000</v>
-      </c>
+      <c r="C155" s="2" t="n">
+        <v>23850000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Guliston Agro MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>388866289</t>
+          <t>264947930</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000479947758001</t>
+          <t>20208000380258936001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3467 10.09.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №1450</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>57565000</v>
+        <v>63700000</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B156" t="n">
-        <v>248</v>
-      </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>1020000</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>293657039</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000215705847001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №4983 от 10.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>58585000</v>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="n">
+        <v>704018000</v>
+      </c>
+      <c r="D156" s="4" t="n">
+        <v>701918000</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B157" t="n">
-        <v>249</v>
-      </c>
-      <c r="C157" s="2" t="n">
-        <v>5193000</v>
-      </c>
-      <c r="D157" s="2" t="n"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Kattaqo'rg'on Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>232795103</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000916787847001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №119/26</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>53392000</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B158" t="n">
-        <v>250</v>
-      </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>2189000</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>293657039</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000215705847001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №36/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>55581000</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B159" t="n">
-        <v>251</v>
-      </c>
-      <c r="C159" s="2" t="n"/>
-      <c r="D159" s="2" t="n">
-        <v>15844000</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Buxoro Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>217182096</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>20208000741938834001</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по дог. №282/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>71425000</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B160" t="n">
-        <v>252</v>
-      </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>9388000</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Mehnat Poligraf MChJ</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>239039600</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>20208000785864823001</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4311</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="n">
-        <v>80813000</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B161" t="n">
-        <v>253</v>
-      </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>6067000</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>293657039</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000215705847001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, h/f №3071 14.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>86880000</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B162" t="n">
-        <v>254</v>
-      </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>2129000</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>293657039</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000215705847001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Shartnoma №281/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>89009000</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B163" t="n">
-        <v>255</v>
-      </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>1973000</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>293657039</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000215705847001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lo, shartnoma №37/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>90982000</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B164" t="n">
-        <v>256</v>
-      </c>
-      <c r="C164" s="2" t="n"/>
-      <c r="D164" s="2" t="n">
-        <v>1142000</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>293657039</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>20208000215705847001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №258/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>92124000</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B165" t="n">
-        <v>257</v>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>1771000</v>
-      </c>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Avgust oyi uchun ijtimoiy soliq</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>90353000</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B166" t="n">
-        <v>258</v>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>1771000</v>
-      </c>
-      <c r="D166" s="2" t="n"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>JShDS avgust oyi uchun</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="n">
-        <v>88582000</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B167" t="n">
-        <v>259</v>
-      </c>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n">
-        <v>1191000</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Navoiy Metall AJ</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>275025945</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000064684166001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Shartnoma №289/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="n">
-        <v>89773000</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B168" t="n">
-        <v>260</v>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>10604000</v>
-      </c>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Durdona Qog'oz MChJ</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>236906530</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>20208000893254047001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №6565</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="n">
-        <v>79169000</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B169" t="n">
-        <v>261</v>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>7353000</v>
-      </c>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>238744455</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>20208000629787199001</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №3249</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="n">
-        <v>71816000</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B170" t="n">
-        <v>262</v>
-      </c>
-      <c r="C170" s="2" t="n"/>
-      <c r="D170" s="2" t="n">
-        <v>21726000</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>293657039</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20208000215705847001</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Shartnoma №182/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="n">
-        <v>93542000</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B171" t="n">
-        <v>263</v>
-      </c>
-      <c r="C171" s="2" t="n"/>
-      <c r="D171" s="2" t="n">
-        <v>624000</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>293657039</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000215705847001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>Shartnoma №93/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="n">
-        <v>94166000</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B172" t="n">
-        <v>264</v>
-      </c>
-      <c r="C172" s="2" t="n">
-        <v>4348000</v>
-      </c>
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>238744455</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000629787199001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №267/26</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="n">
-        <v>89818000</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B173" t="n">
-        <v>265</v>
-      </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>2391000</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Navoiy Metall AJ</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>275025945</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000064684166001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №263/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="n">
-        <v>92209000</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B174" t="n">
-        <v>266</v>
-      </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n">
-        <v>1994000</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>293657039</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000215705847001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8059</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="n">
-        <v>94203000</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B175" t="n">
-        <v>267</v>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>3099000</v>
-      </c>
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>238744455</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000629787199001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №245/26, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="n">
-        <v>91104000</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B176" t="n">
-        <v>268</v>
-      </c>
-      <c r="C176" s="2" t="n">
-        <v>3526000</v>
-      </c>
-      <c r="D176" s="2" t="n"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>238744455</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000629787199001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №137/26</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="n">
-        <v>87578000</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B177" t="n">
-        <v>269</v>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v>6531000</v>
-      </c>
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>238744455</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>20208000629787199001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №1700</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="n">
-        <v>81047000</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B178" t="n">
-        <v>270</v>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>13375000</v>
-      </c>
-      <c r="D178" s="2" t="n"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Durdona Qog'oz MChJ</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>236906530</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000893254047001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №254/26 от 21.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="n">
-        <v>67672000</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B179" t="n">
-        <v>271</v>
-      </c>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n">
-        <v>1087000</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Lazzat Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>224425383</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>20208000457145574001</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №298/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="n">
-        <v>68759000</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B180" t="n">
-        <v>272</v>
-      </c>
-      <c r="C180" s="2" t="n">
-        <v>5407000</v>
-      </c>
-      <c r="D180" s="2" t="n"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>238744455</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>20208000629787199001</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №17/26</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="n">
-        <v>63352000</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B181" t="n">
-        <v>273</v>
-      </c>
-      <c r="C181" s="2" t="n">
-        <v>2995000</v>
-      </c>
-      <c r="D181" s="2" t="n"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>QQS avgust 2026 uchun</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="n">
-        <v>60357000</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B182" t="n">
-        <v>274</v>
-      </c>
-      <c r="C182" s="2" t="n"/>
-      <c r="D182" s="2" t="n">
-        <v>84231000</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Zafar Tikuv MChJ</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>355019763</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>20208000484472803001</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3152</t>
-        </is>
-      </c>
-      <c r="J182" s="2" t="n">
-        <v>144588000</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B183" t="n">
-        <v>275</v>
-      </c>
-      <c r="C183" s="2" t="n">
-        <v>23733000</v>
-      </c>
-      <c r="D183" s="2" t="n"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>238744455</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>20208000629787199001</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №158/26</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="n">
-        <v>120855000</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B184" t="n">
-        <v>276</v>
-      </c>
-      <c r="C184" s="2" t="n">
-        <v>82220000</v>
-      </c>
-      <c r="D184" s="2" t="n"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Buxoro Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>238744455</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>20208000629787199001</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №9905</t>
-        </is>
-      </c>
-      <c r="J184" s="2" t="n">
-        <v>38635000</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B185" t="n">
-        <v>277</v>
-      </c>
-      <c r="C185" s="2" t="n"/>
-      <c r="D185" s="2" t="n">
-        <v>692000</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Navoiy Metall AJ</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>275025945</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>20208000064684166001</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Shartnoma №252/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="n">
-        <v>39327000</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B186" t="n">
-        <v>278</v>
-      </c>
-      <c r="C186" s="2" t="n"/>
-      <c r="D186" s="2" t="n">
-        <v>14080000</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Navoiy Metall AJ</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>275025945</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>20208000064684166001</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №35/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="n">
-        <v>53407000</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B187" t="n">
-        <v>279</v>
-      </c>
-      <c r="C187" s="2" t="n"/>
-      <c r="D187" s="2" t="n">
-        <v>7862000</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>293657039</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>20208000215705847001</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №2828 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="n">
-        <v>61269000</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B188" t="n">
-        <v>280</v>
-      </c>
-      <c r="C188" s="2" t="n"/>
-      <c r="D188" s="2" t="n">
-        <v>2163000</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Navoiy Metall AJ</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>275025945</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>20208000064684166001</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №99/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="n">
-        <v>63432000</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B189" t="n">
-        <v>281</v>
-      </c>
-      <c r="C189" s="2" t="n"/>
-      <c r="D189" s="2" t="n">
-        <v>1990000</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Lazzat Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>224425383</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>20208000457145574001</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №117/26 от 28.09.2026</t>
-        </is>
-      </c>
-      <c r="J189" s="2" t="n">
-        <v>65422000</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B190" t="n">
-        <v>282</v>
-      </c>
-      <c r="C190" s="2" t="n"/>
-      <c r="D190" s="2" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Mehnat Poligraf MChJ</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>239039600</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>20208000785864823001</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №737 от 28.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J190" s="2" t="n">
-        <v>67022000</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B191" t="n">
-        <v>283</v>
-      </c>
-      <c r="C191" s="2" t="n"/>
-      <c r="D191" s="2" t="n">
-        <v>1410000</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Chust Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>269530877</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>20208000098978240001</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7376</t>
-        </is>
-      </c>
-      <c r="J191" s="2" t="n">
-        <v>68432000</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B192" t="n">
-        <v>284</v>
-      </c>
-      <c r="C192" s="2" t="n"/>
-      <c r="D192" s="2" t="n">
-        <v>922000</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>293657039</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>20208000215705847001</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1259 28.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J192" s="2" t="n">
-        <v>69354000</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B193" t="n">
-        <v>285</v>
-      </c>
-      <c r="C193" s="2" t="n">
-        <v>1116000</v>
-      </c>
-      <c r="D193" s="2" t="n"/>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>20208000432180980001</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>Оплата за электроэнергию согласно счету</t>
-        </is>
-      </c>
-      <c r="J193" s="2" t="n">
-        <v>68238000</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B194" t="n">
-        <v>286</v>
-      </c>
-      <c r="C194" s="2" t="n">
-        <v>6620000</v>
-      </c>
-      <c r="D194" s="2" t="n"/>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Qarshi Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>366471775</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>20208000865802242001</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartn. №282/26, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J194" s="2" t="n">
-        <v>61618000</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B195" t="n">
-        <v>287</v>
-      </c>
-      <c r="C195" s="2" t="n">
-        <v>13164000</v>
-      </c>
-      <c r="D195" s="2" t="n"/>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Bahor Non AJ</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>311072588</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>20208000137778051001</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTN. №145/26</t>
-        </is>
-      </c>
-      <c r="J195" s="2" t="n">
-        <v>48454000</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B196" t="n">
-        <v>288</v>
-      </c>
-      <c r="C196" s="2" t="n"/>
-      <c r="D196" s="2" t="n">
-        <v>6812000</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Navoiy Metall AJ</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>275025945</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>20208000064684166001</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №695</t>
-        </is>
-      </c>
-      <c r="J196" s="2" t="n">
-        <v>55266000</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B197" t="n">
-        <v>289</v>
-      </c>
-      <c r="C197" s="2" t="n"/>
-      <c r="D197" s="2" t="n">
-        <v>7640000</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Navoiy Metall AJ</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>275025945</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>20208000064684166001</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №936</t>
-        </is>
-      </c>
-      <c r="J197" s="2" t="n">
-        <v>62906000</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B198" t="n">
-        <v>290</v>
-      </c>
-      <c r="C198" s="2" t="n"/>
-      <c r="D198" s="2" t="n">
-        <v>1094000</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Jizzax Savdo XK</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>293657039</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>20208000215705847001</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по дог. №144/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J198" s="2" t="n">
-        <v>64000000</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B199" t="n">
-        <v>291</v>
-      </c>
-      <c r="C199" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D199" s="2" t="n"/>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Bodomzor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
-        </is>
-      </c>
-      <c r="J199" s="2" t="n">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="n">
         <v>63700000</v>
       </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C200" s="4" t="n">
-        <v>704451000</v>
-      </c>
-      <c r="D200" s="4" t="n">
-        <v>702351000</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="n">
-        <v>63700000</v>
-      </c>
-      <c r="D201" s="4" t="n"/>
+      <c r="D157" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
